--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487565_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487565_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5794</v>
+        <v>6.9321</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5189</v>
+        <v>5.1923</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0606</v>
+        <v>1.7398</v>
       </c>
       <c r="G2" t="n">
         <v>2.0885</v>
@@ -610,13 +610,13 @@
         <v>3.917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7002</v>
+        <v>-0.3476</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2122</v>
+        <v>-0.5387</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5119</v>
+        <v>0.1911</v>
       </c>
       <c r="V2" t="n">
         <v>1.2742</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.104</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="n">
-        <v>0.962</v>
+        <v>0.6861</v>
       </c>
       <c r="F3" t="n">
-        <v>0.142</v>
+        <v>0.5639</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1094</v>
+        <v>-0.8137</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.736</v>
+        <v>1.011</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6266</v>
+        <v>-1.8246</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0312</v>
+        <v>0.7332</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2621</v>
+        <v>2.164</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2933</v>
+        <v>-1.4308</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1406</v>
+        <v>-1.5468</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4739</v>
+        <v>-1.153</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6667</v>
+        <v>-0.3938</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5875</v>
+        <v>2.1543</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0175</v>
+        <v>-0.0907</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3017</v>
+        <v>-0.0471</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2842</v>
+        <v>-0.0437</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0509</v>
+        <v>0.9749</v>
       </c>
       <c r="E4" t="n">
-        <v>0.373</v>
+        <v>0.8597</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.1152</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2036</v>
+        <v>-0.1094</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2596</v>
+        <v>-0.736</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.056</v>
+        <v>0.6266</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1214</v>
+        <v>1.0312</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1878</v>
+        <v>-0.2621</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0664</v>
+        <v>1.2933</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0822</v>
+        <v>-1.1406</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.4739</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0104</v>
+        <v>-0.6667</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.094</v>
+        <v>-0.1116</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3982</v>
+        <v>0.1994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3042</v>
+        <v>-0.311</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="W4" t="n">
         <v>0.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6046</v>
+        <v>0.9302</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1744</v>
+        <v>0.68</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4302</v>
+        <v>0.2502</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8137</v>
+        <v>2.2036</v>
       </c>
       <c r="H5" t="n">
-        <v>1.011</v>
+        <v>2.2596</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8246</v>
+        <v>-0.056</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7332</v>
+        <v>2.1214</v>
       </c>
       <c r="K5" t="n">
-        <v>2.164</v>
+        <v>2.1878</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4308</v>
+        <v>-0.0664</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5468</v>
+        <v>0.0822</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.153</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3938</v>
+        <v>0.0104</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1543</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1543</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7361</v>
+        <v>-0.2147</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5587</v>
+        <v>-0.0912</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1773</v>
+        <v>-0.1235</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4972</v>
+        <v>0.7111</v>
       </c>
       <c r="E6" t="n">
         <v>-0.4028</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>1.1139</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2264</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.6293</v>
       </c>
       <c r="T6" t="n">
         <v>-0.09</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7532</v>
+        <v>-0.5393</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,37 +955,37 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2283</v>
+        <v>-0.0292</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5061</v>
+        <v>0.2353</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2778</v>
+        <v>-0.2645</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.171</v>
+        <v>-2.0927</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1082</v>
+        <v>-3.2899</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2792</v>
+        <v>1.1973</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5914</v>
+        <v>1.078</v>
       </c>
       <c r="K7" t="n">
-        <v>4.0778</v>
+        <v>-0.912</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.4865</v>
+        <v>1.99</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7624</v>
+        <v>-3.1707</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9696</v>
+        <v>-2.3779</v>
       </c>
       <c r="O7" t="n">
         <v>-0.7927</v>
@@ -1000,22 +1000,22 @@
         <v>3.3294</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2657</v>
+        <v>-0.895</v>
       </c>
       <c r="T7" t="n">
-        <v>0.894</v>
+        <v>-0.4717</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6282</v>
+        <v>-0.4233</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,37 +1111,37 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5827</v>
+        <v>-0.6776</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1311</v>
+        <v>0.4398</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4517</v>
+        <v>-1.1174</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0927</v>
+        <v>-1.171</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.2899</v>
+        <v>2.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1973</v>
+        <v>-3.2792</v>
       </c>
       <c r="J9" t="n">
-        <v>1.078</v>
+        <v>1.5914</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.912</v>
+        <v>4.0778</v>
       </c>
       <c r="L9" t="n">
-        <v>1.99</v>
+        <v>-2.4865</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1707</v>
+        <v>-2.7624</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.3779</v>
+        <v>-1.9696</v>
       </c>
       <c r="O9" t="n">
         <v>-0.7927</v>
@@ -1156,22 +1156,22 @@
         <v>3.3294</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4485</v>
+        <v>-0.6402</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8381</v>
+        <v>-0.1723</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.4679</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6083</v>
+        <v>-1.2166</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2022</v>
+        <v>-1.1695</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3419</v>
+        <v>-0.2825</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8603</v>
+        <v>-0.887</v>
       </c>
       <c r="G10" t="n">
         <v>1.5003</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2313</v>
+        <v>-0.1986</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4576</v>
+        <v>-0.3982</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2263</v>
+        <v>0.1995</v>
       </c>
       <c r="V10" t="n">
         <v>-1.492</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5291</v>
+        <v>-1.8744</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4667</v>
+        <v>-1.919</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0623</v>
+        <v>0.0446</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1394</v>
@@ -1312,13 +1312,13 @@
         <v>3.5253</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1771</v>
+        <v>-0.1682</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3305</v>
+        <v>-0.1218</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1534</v>
+        <v>-0.0465</v>
       </c>
       <c r="V11" t="n">
         <v>1.8249</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.690999999999999</v>
+        <v>6.988200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1325</v>
+        <v>5.429500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5586</v>
+        <v>1.5587</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7602</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3435999999999999</v>
+        <v>-0.3436000000000003</v>
       </c>
       <c r="I12" t="n">
         <v>-1.4164</v>
@@ -1390,13 +1390,13 @@
         <v>22.5226</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.6524</v>
+        <v>-3.3553</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.088</v>
+        <v>-1.791</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5643</v>
+        <v>-1.5646</v>
       </c>
       <c r="V12" t="n">
         <v>1.3317</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4269</v>
+        <v>4.8338</v>
       </c>
       <c r="E13" t="n">
-        <v>8.6568</v>
+        <v>6.8148</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2299</v>
+        <v>-1.981</v>
       </c>
       <c r="G13" t="n">
         <v>2.4844</v>
@@ -1468,13 +1468,13 @@
         <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8837</v>
+        <v>1.2907</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8348</v>
+        <v>0.9928</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0489</v>
+        <v>0.2979</v>
       </c>
       <c r="V13" t="n">
         <v>0.2754</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.244</v>
+        <v>3.3298</v>
       </c>
       <c r="E14" t="n">
         <v>2.512</v>
       </c>
       <c r="F14" t="n">
-        <v>0.732</v>
+        <v>0.8178</v>
       </c>
       <c r="G14" t="n">
         <v>2.4183</v>
@@ -1546,13 +1546,13 @@
         <v>0.1958</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8257</v>
+        <v>0.9115</v>
       </c>
       <c r="T14" t="n">
         <v>0.5810999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2446</v>
+        <v>0.3304</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2368</v>
+        <v>1.0352</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7737</v>
+        <v>1.9784</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5369</v>
+        <v>-0.9432</v>
       </c>
       <c r="G15" t="n">
         <v>1.6523</v>
@@ -1624,13 +1624,13 @@
         <v>0.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4155</v>
+        <v>0.3829</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1653</v>
+        <v>0.3699</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5807</v>
+        <v>0.0129</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6083</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CAMBON DOMINGUEZ</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4612</v>
+        <v>0.5846</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2141</v>
+        <v>1.4934</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2471</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0873</v>
+        <v>3.8099</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4029</v>
+        <v>2.5615</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4902</v>
+        <v>1.2484</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0637</v>
+        <v>5.6016</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6247</v>
+        <v>3.576</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5610000000000001</v>
+        <v>2.0256</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.151</v>
+        <v>-1.7917</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2218</v>
+        <v>-1.0145</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9292</v>
+        <v>-0.7772</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1751</v>
+        <v>-4.1128</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6837</v>
+        <v>0.3416</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6534</v>
+        <v>0.0047</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3371</v>
+        <v>0.3369</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0576</v>
+        <v>-1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>M. CAMBON DOMINGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9318</v>
+        <v>-0.8446</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6747</v>
+        <v>-0.0095</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6066</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8099</v>
+        <v>-1.0873</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5615</v>
+        <v>0.4029</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2484</v>
+        <v>-1.4902</v>
       </c>
       <c r="J17" t="n">
-        <v>5.6016</v>
+        <v>1.0637</v>
       </c>
       <c r="K17" t="n">
-        <v>3.576</v>
+        <v>1.6247</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0256</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7917</v>
+        <v>-2.151</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0145</v>
+        <v>-1.2218</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7772</v>
+        <v>-0.9292</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.3502</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1128</v>
+        <v>-1.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1749</v>
+        <v>0.3002</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.4488</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3609</v>
+        <v>0.749</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2166</v>
+        <v>-0.0576</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1258</v>
+        <v>-1.0235</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8677</v>
+        <v>-2.7654</v>
       </c>
       <c r="F18" t="n">
         <v>1.7419</v>
@@ -1858,10 +1858,10 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3564</v>
+        <v>0.4587</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U18" t="n">
         <v>0.594</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3129</v>
+        <v>-1.5397</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6761</v>
+        <v>-1.9831</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3632</v>
+        <v>0.4434</v>
       </c>
       <c r="G19" t="n">
         <v>-2.5174</v>
@@ -1936,13 +1936,13 @@
         <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6169</v>
+        <v>0.3901</v>
       </c>
       <c r="T19" t="n">
-        <v>0.207</v>
+        <v>-0.1</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4099</v>
+        <v>0.4901</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1324</v>
+        <v>-1.8402</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0161</v>
+        <v>-1.9137</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1164</v>
+        <v>0.0735</v>
       </c>
       <c r="G20" t="n">
         <v>-0.346</v>
@@ -2014,13 +2014,13 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2196</v>
+        <v>0.0726</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1008</v>
+        <v>0.0891</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>M. QITTANE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8622</v>
+        <v>-2.6548</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2459</v>
+        <v>-0.0198</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3837</v>
+        <v>-2.635</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5805</v>
+        <v>-1.9397</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9187</v>
+        <v>-1.4043</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.5354</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7017</v>
+        <v>-0.046</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1667</v>
+        <v>0.6362</v>
       </c>
       <c r="L21" t="n">
-        <v>0.535</v>
+        <v>-0.6822</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2822</v>
+        <v>-1.8936</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0853</v>
+        <v>-2.0405</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1969</v>
+        <v>0.1468</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1543</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8727</v>
+        <v>-0.3235</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0306</v>
+        <v>-0.2111</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9033</v>
+        <v>-0.1123</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. QITTANE</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1324</v>
+        <v>-2.8327</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2245</v>
+        <v>-3.2459</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9079</v>
+        <v>0.4132</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9397</v>
+        <v>-1.5805</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4043</v>
+        <v>-0.9187</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5354</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.046</v>
+        <v>0.7017</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6362</v>
+        <v>0.1667</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6822</v>
+        <v>0.535</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8936</v>
+        <v>-2.2822</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0405</v>
+        <v>-1.0853</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1468</v>
+        <v>-1.1969</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3917</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.801</v>
+        <v>0.9022</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4158</v>
+        <v>-0.0306</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3852</v>
+        <v>0.9328</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.64</v>
+        <v>-3.6923</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9315</v>
+        <v>-4.4198</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2915</v>
+        <v>0.7275</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9224</v>
@@ -2248,13 +2248,13 @@
         <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0243</v>
+        <v>0.972</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0465</v>
+        <v>0.5581</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0222</v>
+        <v>0.4139</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.691</v>
+        <v>-4.644399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.558699999999998</v>
+        <v>-1.558599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.1325</v>
+        <v>-3.0859</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7601</v>
+        <v>1.760099999999998</v>
       </c>
       <c r="H24" t="n">
         <v>0.3436999999999999</v>
@@ -2314,7 +2314,7 @@
         <v>-10.8533</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.8601</v>
+        <v>-3.860100000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-10.7717</v>
@@ -2326,13 +2326,13 @@
         <v>11.7507</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6524</v>
+        <v>5.699</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5645</v>
+        <v>1.5643</v>
       </c>
       <c r="U24" t="n">
-        <v>2.088</v>
+        <v>4.1347</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3317</v>
